--- a/test-reports/excel/Selenium_Test_Report.xlsx
+++ b/test-reports/excel/Selenium_Test_Report.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>301.10s</t>
+          <t>301.09s</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="H13" s="14" t="n">
-        <v>0.000156660000001807</v>
+        <v>0.0001266200000031859</v>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="11" t="inlineStr">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="H14" s="10" t="n">
-        <v>0.0001337380000023813</v>
+        <v>0.0001020240000002559</v>
       </c>
       <c r="I14" s="7" t="inlineStr"/>
       <c r="J14" s="11" t="inlineStr">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="H15" s="14" t="n">
-        <v>0.0001286890000073981</v>
+        <v>0.0001002129999960744</v>
       </c>
       <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="11" t="inlineStr">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>0.0001229169999987789</v>
+        <v>9.220100000106868e-05</v>
       </c>
       <c r="I16" s="7" t="inlineStr"/>
       <c r="J16" s="11" t="inlineStr">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="H17" s="14" t="n">
-        <v>0.0001308529999874963</v>
+        <v>9.140400000262616e-05</v>
       </c>
       <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="11" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="H18" s="10" t="n">
-        <v>0.0001426440000074081</v>
+        <v>8.691799999382965e-05</v>
       </c>
       <c r="I18" s="7" t="inlineStr"/>
       <c r="J18" s="11" t="inlineStr">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="H19" s="14" t="n">
-        <v>0.0001163760000082448</v>
+        <v>8.592499999338088e-05</v>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
       <c r="J19" s="11" t="inlineStr">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="H20" s="10" t="n">
-        <v>0.0001282169999967664</v>
+        <v>9.880400000383815e-05</v>
       </c>
       <c r="I20" s="7" t="inlineStr"/>
       <c r="J20" s="11" t="inlineStr">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="H21" s="14" t="n">
-        <v>0.0001113360000033481</v>
+        <v>8.661000001097818e-05</v>
       </c>
       <c r="I21" s="4" t="inlineStr"/>
       <c r="J21" s="11" t="inlineStr">
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="H22" s="10" t="n">
-        <v>0.0001149429999998119</v>
+        <v>8.562800000788684e-05</v>
       </c>
       <c r="I22" s="7" t="inlineStr"/>
       <c r="J22" s="11" t="inlineStr">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H23" s="14" t="n">
-        <v>0.0001245609999926955</v>
+        <v>9.577299999818933e-05</v>
       </c>
       <c r="I23" s="4" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr">
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="H24" s="10" t="n">
-        <v>0.0001158640000085143</v>
+        <v>8.683100000439481e-05</v>
       </c>
       <c r="I24" s="7" t="inlineStr"/>
       <c r="J24" s="11" t="inlineStr">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="H25" s="14" t="n">
-        <v>0.0001159650000062129</v>
+        <v>0.0001037330000031034</v>
       </c>
       <c r="I25" s="4" t="inlineStr"/>
       <c r="J25" s="11" t="inlineStr">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>0.0001144820000007485</v>
+        <v>8.518799999990279e-05</v>
       </c>
       <c r="I26" s="7" t="inlineStr"/>
       <c r="J26" s="11" t="inlineStr">
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="H27" s="14" t="n">
-        <v>0.0001225470000036921</v>
+        <v>8.595699999602857e-05</v>
       </c>
       <c r="I27" s="4" t="inlineStr"/>
       <c r="J27" s="11" t="inlineStr">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="H28" s="10" t="n">
-        <v>0.0001432850000071539</v>
+        <v>9.118399999863414e-05</v>
       </c>
       <c r="I28" s="7" t="inlineStr"/>
       <c r="J28" s="11" t="inlineStr">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="H29" s="14" t="n">
-        <v>0.0001140010000000302</v>
+        <v>8.737100000644205e-05</v>
       </c>
       <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>0.0001151130000067724</v>
+        <v>8.799299999395771e-05</v>
       </c>
       <c r="I30" s="7" t="inlineStr"/>
       <c r="J30" s="11" t="inlineStr">
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="H31" s="14" t="n">
-        <v>0.0001273459999993065</v>
+        <v>9.730000000729433e-05</v>
       </c>
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="11" t="inlineStr">
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>0.0001452989999961574</v>
+        <v>0.0001105999999992946</v>
       </c>
       <c r="I32" s="7" t="inlineStr"/>
       <c r="J32" s="11" t="inlineStr">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="H33" s="14" t="n">
-        <v>0.0001129699999893319</v>
+        <v>9.00470000004816e-05</v>
       </c>
       <c r="I33" s="4" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>0.0001095829999968601</v>
+        <v>8.253500000421354e-05</v>
       </c>
       <c r="I34" s="7" t="inlineStr"/>
       <c r="J34" s="11" t="inlineStr">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="H35" s="14" t="n">
-        <v>0.000108961999998769</v>
+        <v>8.201500000382111e-05</v>
       </c>
       <c r="I35" s="4" t="inlineStr"/>
       <c r="J35" s="11" t="inlineStr">
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="H36" s="10" t="n">
-        <v>0.0001306019999987029</v>
+        <v>7.784800000365522e-05</v>
       </c>
       <c r="I36" s="7" t="inlineStr"/>
       <c r="J36" s="11" t="inlineStr">
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="H37" s="14" t="n">
-        <v>0.000112377999997193</v>
+        <v>8.952500000702912e-05</v>
       </c>
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="11" t="inlineStr">
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="H38" s="10" t="n">
-        <v>0.0001067370000100709</v>
+        <v>8.165900000278725e-05</v>
       </c>
       <c r="I38" s="7" t="inlineStr"/>
       <c r="J38" s="11" t="inlineStr">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="H39" s="14" t="n">
-        <v>0.0001054049999993367</v>
+        <v>0.0001182360000058225</v>
       </c>
       <c r="I39" s="4" t="inlineStr"/>
       <c r="J39" s="11" t="inlineStr">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="H40" s="10" t="n">
-        <v>0.0001073279999985743</v>
+        <v>8.065000000101463e-05</v>
       </c>
       <c r="I40" s="7" t="inlineStr"/>
       <c r="J40" s="11" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="H41" s="14" t="n">
-        <v>0.0001113369999927727</v>
+        <v>8.146999999780746e-05</v>
       </c>
       <c r="I41" s="4" t="inlineStr"/>
       <c r="J41" s="11" t="inlineStr">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="H42" s="10" t="n">
-        <v>0.0001090509999954747</v>
+        <v>8.502700001145058e-05</v>
       </c>
       <c r="I42" s="7" t="inlineStr"/>
       <c r="J42" s="11" t="inlineStr">
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="H43" s="14" t="n">
-        <v>0.0001101339999962647</v>
+        <v>7.901400000775993e-05</v>
       </c>
       <c r="I43" s="4" t="inlineStr"/>
       <c r="J43" s="11" t="inlineStr">
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>0.0001105839999979707</v>
+        <v>7.749299999204595e-05</v>
       </c>
       <c r="I44" s="7" t="inlineStr"/>
       <c r="J44" s="11" t="inlineStr">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="H45" s="14" t="n">
-        <v>0.0001072980000031976</v>
+        <v>8.173599999850012e-05</v>
       </c>
       <c r="I45" s="4" t="inlineStr"/>
       <c r="J45" s="11" t="inlineStr">
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="H46" s="10" t="n">
-        <v>0.0001124380000021574</v>
+        <v>8.366400000170415e-05</v>
       </c>
       <c r="I46" s="7" t="inlineStr"/>
       <c r="J46" s="11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="H47" s="14" t="n">
-        <v>0.0001066870000130393</v>
+        <v>8.055699998976706e-05</v>
       </c>
       <c r="I47" s="4" t="inlineStr"/>
       <c r="J47" s="11" t="inlineStr">
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>0.0001357019999943532</v>
+        <v>0.0001028579999911017</v>
       </c>
       <c r="I48" s="7" t="inlineStr"/>
       <c r="J48" s="11" t="inlineStr">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="H49" s="14" t="n">
-        <v>0.0001237289999949098</v>
+        <v>9.308500000315689e-05</v>
       </c>
       <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="11" t="inlineStr">
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="H50" s="10" t="n">
-        <v>0.0001215850000022556</v>
+        <v>9.443000000430857e-05</v>
       </c>
       <c r="I50" s="7" t="inlineStr"/>
       <c r="J50" s="11" t="inlineStr">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="H51" s="14" t="n">
-        <v>0.0001825980000091931</v>
+        <v>0.0001549109999956499</v>
       </c>
       <c r="I51" s="4" t="inlineStr"/>
       <c r="J51" s="11" t="inlineStr">
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="H52" s="10" t="n">
-        <v>0.0001229570000020885</v>
+        <v>9.801899999217767e-05</v>
       </c>
       <c r="I52" s="7" t="inlineStr"/>
       <c r="J52" s="11" t="inlineStr">
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="H53" s="14" t="n">
-        <v>0.0001473129999993716</v>
+        <v>9.531300000276133e-05</v>
       </c>
       <c r="I53" s="4" t="inlineStr"/>
       <c r="J53" s="11" t="inlineStr">
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="H54" s="10" t="n">
-        <v>0.0001653350000054843</v>
+        <v>9.319999999490847e-05</v>
       </c>
       <c r="I54" s="7" t="inlineStr"/>
       <c r="J54" s="11" t="inlineStr">
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0.0001290889999978617</v>
+        <v>9.907900000882819e-05</v>
       </c>
       <c r="I55" s="4" t="inlineStr"/>
       <c r="J55" s="11" t="inlineStr">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H56" s="10" t="n">
-        <v>0.0001253819999931238</v>
+        <v>9.661800000060339e-05</v>
       </c>
       <c r="I56" s="7" t="inlineStr"/>
       <c r="J56" s="11" t="inlineStr">
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="H57" s="14" t="n">
-        <v>0.0001241500000048745</v>
+        <v>9.670000000028267e-05</v>
       </c>
       <c r="I57" s="4" t="inlineStr"/>
       <c r="J57" s="11" t="inlineStr">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="H58" s="10" t="n">
-        <v>0.0001167759999987084</v>
+        <v>8.889199999373432e-05</v>
       </c>
       <c r="I58" s="7" t="inlineStr"/>
       <c r="J58" s="11" t="inlineStr">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="H59" s="14" t="n">
-        <v>0.0001181789999975535</v>
+        <v>0.0001026919999986831</v>
       </c>
       <c r="I59" s="4" t="inlineStr"/>
       <c r="J59" s="11" t="inlineStr">
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="H60" s="10" t="n">
-        <v>0.0001212349999946127</v>
+        <v>8.991899998989084e-05</v>
       </c>
       <c r="I60" s="7" t="inlineStr"/>
       <c r="J60" s="11" t="inlineStr">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="H61" s="14" t="n">
-        <v>0.0001254720000076759</v>
+        <v>9.221700000239252e-05</v>
       </c>
       <c r="I61" s="4" t="inlineStr"/>
       <c r="J61" s="11" t="inlineStr">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="H62" s="10" t="n">
-        <v>0.0001446979999997211</v>
+        <v>9.29830000018228e-05</v>
       </c>
       <c r="I62" s="7" t="inlineStr"/>
       <c r="J62" s="11" t="inlineStr">
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="H63" s="14" t="n">
-        <v>0.0001082709999877807</v>
+        <v>8.02870000029543e-05</v>
       </c>
       <c r="I63" s="4" t="inlineStr"/>
       <c r="J63" s="11" t="inlineStr">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="H64" s="10" t="n">
-        <v>0.0001072489999955906</v>
+        <v>7.956700000022465e-05</v>
       </c>
       <c r="I64" s="7" t="inlineStr"/>
       <c r="J64" s="11" t="inlineStr">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="H65" s="14" t="n">
-        <v>0.0001108949999917286</v>
+        <v>8.806599998933962e-05</v>
       </c>
       <c r="I65" s="4" t="inlineStr"/>
       <c r="J65" s="11" t="inlineStr">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="H66" s="10" t="n">
-        <v>0.0001130590000002485</v>
+        <v>8.883299999240535e-05</v>
       </c>
       <c r="I66" s="7" t="inlineStr"/>
       <c r="J66" s="11" t="inlineStr">
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="H67" s="14" t="n">
-        <v>0.0001088719999984278</v>
+        <v>8.082300000467058e-05</v>
       </c>
       <c r="I67" s="4" t="inlineStr"/>
       <c r="J67" s="11" t="inlineStr">
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="H68" s="10" t="n">
-        <v>0.0001079900000036105</v>
+        <v>8.05879999887793e-05</v>
       </c>
       <c r="I68" s="7" t="inlineStr"/>
       <c r="J68" s="11" t="inlineStr">
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="H69" s="14" t="n">
-        <v>0.0001130389999985937</v>
+        <v>9.366800000520925e-05</v>
       </c>
       <c r="I69" s="4" t="inlineStr"/>
       <c r="J69" s="11" t="inlineStr">
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="H70" s="10" t="n">
-        <v>0.0001297489999956269</v>
+        <v>8.598799999504081e-05</v>
       </c>
       <c r="I70" s="7" t="inlineStr"/>
       <c r="J70" s="11" t="inlineStr">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="H71" s="14" t="n">
-        <v>0.0001298399999996036</v>
+        <v>8.064600000068367e-05</v>
       </c>
       <c r="I71" s="4" t="inlineStr"/>
       <c r="J71" s="11" t="inlineStr">
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="H72" s="10" t="n">
-        <v>0.0001079900000036105</v>
+        <v>8.099699999775112e-05</v>
       </c>
       <c r="I72" s="7" t="inlineStr"/>
       <c r="J72" s="11" t="inlineStr">
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="H73" s="14" t="n">
-        <v>0.0001068979999985231</v>
+        <v>7.823900000403228e-05</v>
       </c>
       <c r="I73" s="4" t="inlineStr"/>
       <c r="J73" s="11" t="inlineStr">
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="H74" s="10" t="n">
-        <v>0.0001127689999975701</v>
+        <v>7.918999999390053e-05</v>
       </c>
       <c r="I74" s="7" t="inlineStr"/>
       <c r="J74" s="11" t="inlineStr">
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="H75" s="14" t="n">
-        <v>0.0001131900000075348</v>
+        <v>8.787699999857068e-05</v>
       </c>
       <c r="I75" s="4" t="inlineStr"/>
       <c r="J75" s="11" t="inlineStr">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="H76" s="10" t="n">
-        <v>0.0001123979999988478</v>
+        <v>8.334099999274258e-05</v>
       </c>
       <c r="I76" s="7" t="inlineStr"/>
       <c r="J76" s="11" t="inlineStr">
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="H77" s="14" t="n">
-        <v>0.0001108050000055982</v>
+        <v>7.987800000819334e-05</v>
       </c>
       <c r="I77" s="4" t="inlineStr"/>
       <c r="J77" s="11" t="inlineStr">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="H78" s="10" t="n">
-        <v>0.0001335170000089647</v>
+        <v>8.016600000360086e-05</v>
       </c>
       <c r="I78" s="7" t="inlineStr"/>
       <c r="J78" s="11" t="inlineStr">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="H79" s="14" t="n">
-        <v>0.0002045079999959398</v>
+        <v>8.094000000369306e-05</v>
       </c>
       <c r="I79" s="4" t="inlineStr"/>
       <c r="J79" s="11" t="inlineStr">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="H80" s="10" t="n">
-        <v>0.0001098329999962289</v>
+        <v>8.019099999501123e-05</v>
       </c>
       <c r="I80" s="7" t="inlineStr"/>
       <c r="J80" s="11" t="inlineStr">
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="H81" s="14" t="n">
-        <v>0.0001098840000111068</v>
+        <v>8.027299999469051e-05</v>
       </c>
       <c r="I81" s="4" t="inlineStr"/>
       <c r="J81" s="11" t="inlineStr">
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="H82" s="10" t="n">
-        <v>0.0001080090000016298</v>
+        <v>9.149500000660282e-05</v>
       </c>
       <c r="I82" s="7" t="inlineStr"/>
       <c r="J82" s="11" t="inlineStr">
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="H83" s="14" t="n">
-        <v>0.0001898109999984854</v>
+        <v>0.000149030000002881</v>
       </c>
       <c r="I83" s="4" t="inlineStr"/>
       <c r="J83" s="11" t="inlineStr">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="H84" s="10" t="n">
-        <v>0.0002449739999974554</v>
+        <v>9.590999999886662e-05</v>
       </c>
       <c r="I84" s="7" t="inlineStr"/>
       <c r="J84" s="11" t="inlineStr">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="H85" s="14" t="n">
-        <v>0.0001869569999968235</v>
+        <v>9.460900000135553e-05</v>
       </c>
       <c r="I85" s="4" t="inlineStr"/>
       <c r="J85" s="11" t="inlineStr">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="H86" s="10" t="n">
-        <v>0.0002272910000016282</v>
+        <v>8.678700000075423e-05</v>
       </c>
       <c r="I86" s="7" t="inlineStr"/>
       <c r="J86" s="11" t="inlineStr">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="H87" s="14" t="n">
-        <v>0.000182116999994264</v>
+        <v>9.183599999573744e-05</v>
       </c>
       <c r="I87" s="4" t="inlineStr"/>
       <c r="J87" s="11" t="inlineStr">
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="H88" s="10" t="n">
-        <v>0.0001488660000035225</v>
+        <v>0.0001411380000035933</v>
       </c>
       <c r="I88" s="7" t="inlineStr"/>
       <c r="J88" s="11" t="inlineStr">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H89" s="14" t="n">
-        <v>0.0001304710000056275</v>
+        <v>0.000100372999995102</v>
       </c>
       <c r="I89" s="4" t="inlineStr"/>
       <c r="J89" s="11" t="inlineStr">
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="H90" s="10" t="n">
-        <v>0.0001275560000095766</v>
+        <v>9.461900000928836e-05</v>
       </c>
       <c r="I90" s="7" t="inlineStr"/>
       <c r="J90" s="11" t="inlineStr">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="H91" s="14" t="n">
-        <v>0.0001209839999916085</v>
+        <v>9.24360000027491e-05</v>
       </c>
       <c r="I91" s="4" t="inlineStr"/>
       <c r="J91" s="11" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="H92" s="10" t="n">
-        <v>0.0001181380000048193</v>
+        <v>8.704500000078497e-05</v>
       </c>
       <c r="I92" s="7" t="inlineStr"/>
       <c r="J92" s="11" t="inlineStr">
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="H93" s="14" t="n">
-        <v>0.000118869999994331</v>
+        <v>8.691599998655875e-05</v>
       </c>
       <c r="I93" s="4" t="inlineStr"/>
       <c r="J93" s="11" t="inlineStr">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="H94" s="10" t="n">
-        <v>0.0001128399999998919</v>
+        <v>8.61240000062935e-05</v>
       </c>
       <c r="I94" s="7" t="inlineStr"/>
       <c r="J94" s="11" t="inlineStr">
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="H95" s="14" t="n">
-        <v>0.0001125879999932522</v>
+        <v>7.915500000876818e-05</v>
       </c>
       <c r="I95" s="4" t="inlineStr"/>
       <c r="J95" s="11" t="inlineStr">
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="H96" s="10" t="n">
-        <v>0.0001125180000087767</v>
+        <v>8.024999999634019e-05</v>
       </c>
       <c r="I96" s="7" t="inlineStr"/>
       <c r="J96" s="11" t="inlineStr">
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="H97" s="14" t="n">
-        <v>0.0001169659999931127</v>
+        <v>8.316099999206017e-05</v>
       </c>
       <c r="I97" s="4" t="inlineStr"/>
       <c r="J97" s="11" t="inlineStr">
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="H98" s="10" t="n">
-        <v>0.0001413319999983287</v>
+        <v>0.0001015070000107698</v>
       </c>
       <c r="I98" s="7" t="inlineStr"/>
       <c r="J98" s="11" t="inlineStr">
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="H99" s="14" t="n">
-        <v>0.000112318999995864</v>
+        <v>7.97959999943032e-05</v>
       </c>
       <c r="I99" s="4" t="inlineStr"/>
       <c r="J99" s="11" t="inlineStr">
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="H100" s="10" t="n">
-        <v>0.0001109049999996614</v>
+        <v>8.318700000131685e-05</v>
       </c>
       <c r="I100" s="7" t="inlineStr"/>
       <c r="J100" s="11" t="inlineStr">
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="H101" s="14" t="n">
-        <v>0.0001100440000101344</v>
+        <v>8.387900000172976e-05</v>
       </c>
       <c r="I101" s="4" t="inlineStr"/>
       <c r="J101" s="11" t="inlineStr">
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="H102" s="10" t="n">
-        <v>0.0001152230000087684</v>
+        <v>8.199699999522636e-05</v>
       </c>
       <c r="I102" s="7" t="inlineStr"/>
       <c r="J102" s="11" t="inlineStr">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="H103" s="14" t="n">
-        <v>0.0001078899999953364</v>
+        <v>8.210999999391788e-05</v>
       </c>
       <c r="I103" s="4" t="inlineStr"/>
       <c r="J103" s="11" t="inlineStr">
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="H104" s="10" t="n">
-        <v>0.0001116369999891731</v>
+        <v>8.180399998991561e-05</v>
       </c>
       <c r="I104" s="7" t="inlineStr"/>
       <c r="J104" s="11" t="inlineStr">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="H105" s="14" t="n">
-        <v>0.000111798000006047</v>
+        <v>8.018699999468026e-05</v>
       </c>
       <c r="I105" s="4" t="inlineStr"/>
       <c r="J105" s="11" t="inlineStr">
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="H106" s="10" t="n">
-        <v>0.0001350000000002183</v>
+        <v>7.945799998765324e-05</v>
       </c>
       <c r="I106" s="7" t="inlineStr"/>
       <c r="J106" s="11" t="inlineStr">
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="H107" s="14" t="n">
-        <v>0.0001322650000048498</v>
+        <v>8.319500000197877e-05</v>
       </c>
       <c r="I107" s="4" t="inlineStr"/>
       <c r="J107" s="11" t="inlineStr">
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="H108" s="10" t="n">
-        <v>0.0001606979999877467</v>
+        <v>0.0001448510000017222</v>
       </c>
       <c r="I108" s="7" t="inlineStr"/>
       <c r="J108" s="11" t="inlineStr">
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="H109" s="14" t="n">
-        <v>0.0001077290000068842</v>
+        <v>8.439799999848674e-05</v>
       </c>
       <c r="I109" s="4" t="inlineStr"/>
       <c r="J109" s="11" t="inlineStr">
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="H110" s="10" t="n">
-        <v>0.0001087709999865183</v>
+        <v>8.134200000142755e-05</v>
       </c>
       <c r="I110" s="7" t="inlineStr"/>
       <c r="J110" s="11" t="inlineStr">
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="H111" s="14" t="n">
-        <v>0.0001134299999989707</v>
+        <v>8.112899999446199e-05</v>
       </c>
       <c r="I111" s="4" t="inlineStr"/>
       <c r="J111" s="11" t="inlineStr">
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="H112" s="10" t="n">
-        <v>0.0001191300000016327</v>
+        <v>8.690100000308121e-05</v>
       </c>
       <c r="I112" s="7" t="inlineStr"/>
       <c r="J112" s="11" t="inlineStr">
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="H113" s="14" t="n">
-        <v>0.0001114860000086537</v>
+        <v>8.057700000563273e-05</v>
       </c>
       <c r="I113" s="4" t="inlineStr"/>
       <c r="J113" s="11" t="inlineStr">
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="H114" s="10" t="n">
-        <v>0.000131443000000786</v>
+        <v>7.957399999725112e-05</v>
       </c>
       <c r="I114" s="7" t="inlineStr"/>
       <c r="J114" s="11" t="inlineStr">
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="H115" s="14" t="n">
-        <v>0.0001084409999947411</v>
+        <v>7.973099999958322e-05</v>
       </c>
       <c r="I115" s="4" t="inlineStr"/>
       <c r="J115" s="11" t="inlineStr">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="H116" s="10" t="n">
-        <v>0.0001128690000058441</v>
+        <v>7.896500000015294e-05</v>
       </c>
       <c r="I116" s="7" t="inlineStr"/>
       <c r="J116" s="11" t="inlineStr">
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="H117" s="14" t="n">
-        <v>0.0001073779999956059</v>
+        <v>8.611100000166516e-05</v>
       </c>
       <c r="I117" s="4" t="inlineStr"/>
       <c r="J117" s="11" t="inlineStr">
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="H118" s="10" t="n">
-        <v>0.0001113360000033481</v>
+        <v>9.207800000865518e-05</v>
       </c>
       <c r="I118" s="7" t="inlineStr"/>
       <c r="J118" s="11" t="inlineStr">
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="H119" s="14" t="n">
-        <v>0.0001088010000103168</v>
+        <v>7.855500000175653e-05</v>
       </c>
       <c r="I119" s="4" t="inlineStr"/>
       <c r="J119" s="11" t="inlineStr">
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="H120" s="10" t="n">
-        <v>0.0001098840000111068</v>
+        <v>8.092699999906472e-05</v>
       </c>
       <c r="I120" s="7" t="inlineStr"/>
       <c r="J120" s="11" t="inlineStr">
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="H121" s="14" t="n">
-        <v>0.0001176880000031133</v>
+        <v>9.898999999791158e-05</v>
       </c>
       <c r="I121" s="4" t="inlineStr"/>
       <c r="J121" s="11" t="inlineStr">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H122" s="10" t="n">
-        <v>0.000186945999999466</v>
+        <v>0.0001396180000057257</v>
       </c>
       <c r="I122" s="7" t="inlineStr"/>
       <c r="J122" s="11" t="inlineStr">
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="H123" s="14" t="n">
-        <v>0.0001081900000059477</v>
+        <v>8.351799999672949e-05</v>
       </c>
       <c r="I123" s="4" t="inlineStr"/>
       <c r="J123" s="11" t="inlineStr">
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="H124" s="10" t="n">
-        <v>0.0001093719999971654</v>
+        <v>8.094000000369306e-05</v>
       </c>
       <c r="I124" s="7" t="inlineStr"/>
       <c r="J124" s="11" t="inlineStr">
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="H125" s="14" t="n">
-        <v>0.0001172460000020692</v>
+        <v>8.367699999212164e-05</v>
       </c>
       <c r="I125" s="4" t="inlineStr"/>
       <c r="J125" s="11" t="inlineStr">
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="H126" s="10" t="n">
-        <v>0.0001144320000037169</v>
+        <v>8.436499999220359e-05</v>
       </c>
       <c r="I126" s="7" t="inlineStr"/>
       <c r="J126" s="11" t="inlineStr">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="H127" s="14" t="n">
-        <v>0.0001130990000035581</v>
+        <v>8.76020000077915e-05</v>
       </c>
       <c r="I127" s="4" t="inlineStr"/>
       <c r="J127" s="11" t="inlineStr">
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="H128" s="10" t="n">
-        <v>0.0001079200000049241</v>
+        <v>8.029199999270986e-05</v>
       </c>
       <c r="I128" s="7" t="inlineStr"/>
       <c r="J128" s="11" t="inlineStr">
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="H129" s="14" t="n">
-        <v>0.0001191900000065971</v>
+        <v>8.272300000555788e-05</v>
       </c>
       <c r="I129" s="4" t="inlineStr"/>
       <c r="J129" s="11" t="inlineStr">
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="H130" s="10" t="n">
-        <v>0.0001459099999863156</v>
+        <v>7.904299999950126e-05</v>
       </c>
       <c r="I130" s="7" t="inlineStr"/>
       <c r="J130" s="11" t="inlineStr">
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="H131" s="14" t="n">
-        <v>0.0001142119999997249</v>
+        <v>9.25269999925149e-05</v>
       </c>
       <c r="I131" s="4" t="inlineStr"/>
       <c r="J131" s="11" t="inlineStr">
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="H132" s="10" t="n">
-        <v>0.0001083000000079437</v>
+        <v>8.097799999973176e-05</v>
       </c>
       <c r="I132" s="7" t="inlineStr"/>
       <c r="J132" s="11" t="inlineStr">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="H133" s="14" t="n">
-        <v>0.0001085809999921139</v>
+        <v>8.022999999468539e-05</v>
       </c>
       <c r="I133" s="4" t="inlineStr"/>
       <c r="J133" s="11" t="inlineStr">
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="H134" s="10" t="n">
-        <v>0.0001085810000063248</v>
+        <v>8.147100000144292e-05</v>
       </c>
       <c r="I134" s="7" t="inlineStr"/>
       <c r="J134" s="11" t="inlineStr">
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="H135" s="14" t="n">
-        <v>0.00011988200000701</v>
+        <v>8.24669999985872e-05</v>
       </c>
       <c r="I135" s="4" t="inlineStr"/>
       <c r="J135" s="11" t="inlineStr">
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="H136" s="10" t="n">
-        <v>0.001014237000006801</v>
+        <v>0.0007782069999962005</v>
       </c>
       <c r="I136" s="7" t="inlineStr"/>
       <c r="J136" s="11" t="inlineStr">
@@ -7444,7 +7444,7 @@
         </is>
       </c>
       <c r="H137" s="14" t="n">
-        <v>0.0001416919999996935</v>
+        <v>8.609799999703682e-05</v>
       </c>
       <c r="I137" s="4" t="inlineStr"/>
       <c r="J137" s="11" t="inlineStr">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="H138" s="10" t="n">
-        <v>0.0001094520000037846</v>
+        <v>8.882400000231883e-05</v>
       </c>
       <c r="I138" s="7" t="inlineStr"/>
       <c r="J138" s="11" t="inlineStr">
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="H139" s="14" t="n">
-        <v>0.0001147530000054076</v>
+        <v>8.42099999971424e-05</v>
       </c>
       <c r="I139" s="4" t="inlineStr"/>
       <c r="J139" s="11" t="inlineStr">
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="H140" s="10" t="n">
-        <v>0.0001091520000073842</v>
+        <v>8.248999999693751e-05</v>
       </c>
       <c r="I140" s="7" t="inlineStr"/>
       <c r="J140" s="11" t="inlineStr">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="H141" s="14" t="n">
-        <v>0.0001147819999971489</v>
+        <v>8.365099999707581e-05</v>
       </c>
       <c r="I141" s="4" t="inlineStr"/>
       <c r="J141" s="11" t="inlineStr">
@@ -7674,7 +7674,7 @@
         </is>
       </c>
       <c r="H142" s="10" t="n">
-        <v>0.0001083899999940741</v>
+        <v>8.102099999973689e-05</v>
       </c>
       <c r="I142" s="7" t="inlineStr"/>
       <c r="J142" s="11" t="inlineStr">
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="H143" s="14" t="n">
-        <v>0.0001236789999978782</v>
+        <v>8.829399999399357e-05</v>
       </c>
       <c r="I143" s="4" t="inlineStr"/>
       <c r="J143" s="11" t="inlineStr">
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="H144" s="10" t="n">
-        <v>0.0001180890000114232</v>
+        <v>9.470999999905416e-05</v>
       </c>
       <c r="I144" s="7" t="inlineStr"/>
       <c r="J144" s="11" t="inlineStr">
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="H145" s="14" t="n">
-        <v>0.0001396579999948244</v>
+        <v>8.600099999966915e-05</v>
       </c>
       <c r="I145" s="4" t="inlineStr"/>
       <c r="J145" s="11" t="inlineStr">
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="H146" s="10" t="n">
-        <v>0.000112778999991292</v>
+        <v>8.381600000006983e-05</v>
       </c>
       <c r="I146" s="7" t="inlineStr"/>
       <c r="J146" s="11" t="inlineStr">
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="H147" s="14" t="n">
-        <v>0.0001095630000094161</v>
+        <v>0.0001071659999922758</v>
       </c>
       <c r="I147" s="4" t="inlineStr"/>
       <c r="J147" s="11" t="inlineStr">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="H148" s="10" t="n">
-        <v>0.0001185490000068512</v>
+        <v>0.0001299479999943287</v>
       </c>
       <c r="I148" s="7" t="inlineStr"/>
       <c r="J148" s="11" t="inlineStr">
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="H149" s="14" t="n">
-        <v>0.0001125090000044793</v>
+        <v>0.0001058249999914551</v>
       </c>
       <c r="I149" s="4" t="inlineStr"/>
       <c r="J149" s="11" t="inlineStr">
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="H150" s="10" t="n">
-        <v>0.0001678609999942182</v>
+        <v>0.0001694930000013528</v>
       </c>
       <c r="I150" s="7" t="inlineStr"/>
       <c r="J150" s="11" t="inlineStr">
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="H151" s="14" t="n">
-        <v>0.0001100930000035305</v>
+        <v>9.835999999552314e-05</v>
       </c>
       <c r="I151" s="4" t="inlineStr"/>
       <c r="J151" s="11" t="inlineStr">
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="H152" s="10" t="n">
-        <v>0.000110825000007253</v>
+        <v>9.801000000209115e-05</v>
       </c>
       <c r="I152" s="7" t="inlineStr"/>
       <c r="J152" s="11" t="inlineStr">
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="H153" s="14" t="n">
-        <v>0.0001181379999906085</v>
+        <v>8.996200000410681e-05</v>
       </c>
       <c r="I153" s="4" t="inlineStr"/>
       <c r="J153" s="11" t="inlineStr">
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="H154" s="10" t="n">
-        <v>0.0001338379999964445</v>
+        <v>8.335500000100637e-05</v>
       </c>
       <c r="I154" s="7" t="inlineStr"/>
       <c r="J154" s="11" t="inlineStr">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H155" s="14" t="n">
-        <v>0.0001113060000079713</v>
+        <v>8.363399999211651e-05</v>
       </c>
       <c r="I155" s="4" t="inlineStr"/>
       <c r="J155" s="11" t="inlineStr">
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="H156" s="10" t="n">
-        <v>0.0001104840000039076</v>
+        <v>8.371399999873574e-05</v>
       </c>
       <c r="I156" s="7" t="inlineStr"/>
       <c r="J156" s="11" t="inlineStr">
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="H157" s="14" t="n">
-        <v>0.0001167860000066412</v>
+        <v>8.288099999731458e-05</v>
       </c>
       <c r="I157" s="4" t="inlineStr"/>
       <c r="J157" s="11" t="inlineStr">
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="H158" s="10" t="n">
-        <v>0.0001107550000085666</v>
+        <v>9.874500000250919e-05</v>
       </c>
       <c r="I158" s="7" t="inlineStr"/>
       <c r="J158" s="11" t="inlineStr">
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="H159" s="14" t="n">
-        <v>0.0001079500000003009</v>
+        <v>7.893999999453172e-05</v>
       </c>
       <c r="I159" s="4" t="inlineStr"/>
       <c r="J159" s="11" t="inlineStr">
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="H160" s="10" t="n">
-        <v>0.0001124779999912562</v>
+        <v>8.479699999952572e-05</v>
       </c>
       <c r="I160" s="7" t="inlineStr"/>
       <c r="J160" s="11" t="inlineStr">
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="H161" s="14" t="n">
-        <v>0.0001211249999926167</v>
+        <v>8.883099999934529e-05</v>
       </c>
       <c r="I161" s="4" t="inlineStr"/>
       <c r="J161" s="11" t="inlineStr">
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="H162" s="10" t="n">
-        <v>0.0001425939999961656</v>
+        <v>9.037600000283419e-05</v>
       </c>
       <c r="I162" s="7" t="inlineStr"/>
       <c r="J162" s="11" t="inlineStr">
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="H163" s="14" t="n">
-        <v>0.0001089419999971142</v>
+        <v>8.527399999991303e-05</v>
       </c>
       <c r="I163" s="4" t="inlineStr"/>
       <c r="J163" s="11" t="inlineStr">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="H164" s="10" t="n">
-        <v>0.0002892959999911682</v>
+        <v>0.0001413310000089041</v>
       </c>
       <c r="I164" s="7" t="inlineStr"/>
       <c r="J164" s="11" t="inlineStr">
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="H165" s="14" t="n">
-        <v>0.0001646139999991192</v>
+        <v>8.081900000433961e-05</v>
       </c>
       <c r="I165" s="4" t="inlineStr"/>
       <c r="J165" s="11" t="inlineStr">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="H166" s="10" t="n">
-        <v>0.0002044480000051863</v>
+        <v>7.993399999861595e-05</v>
       </c>
       <c r="I166" s="7" t="inlineStr"/>
       <c r="J166" s="11" t="inlineStr">
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="H167" s="14" t="n">
-        <v>0.0001918950000003861</v>
+        <v>0.0001052639999983285</v>
       </c>
       <c r="I167" s="4" t="inlineStr"/>
       <c r="J167" s="11" t="inlineStr">
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="H168" s="10" t="n">
-        <v>0.0001958219999949051</v>
+        <v>0.0001001610000059827</v>
       </c>
       <c r="I168" s="7" t="inlineStr"/>
       <c r="J168" s="11" t="inlineStr">
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="H169" s="14" t="n">
-        <v>0.0001756139999997686</v>
+        <v>8.213799999623461e-05</v>
       </c>
       <c r="I169" s="4" t="inlineStr"/>
       <c r="J169" s="11" t="inlineStr">
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="H170" s="10" t="n">
-        <v>0.0001991580000009208</v>
+        <v>8.22740000074873e-05</v>
       </c>
       <c r="I170" s="7" t="inlineStr"/>
       <c r="J170" s="11" t="inlineStr">
@@ -9008,7 +9008,7 @@
         </is>
       </c>
       <c r="H171" s="14" t="n">
-        <v>0.0001974959999984094</v>
+        <v>8.420599999681144e-05</v>
       </c>
       <c r="I171" s="4" t="inlineStr"/>
       <c r="J171" s="11" t="inlineStr">
@@ -9054,7 +9054,7 @@
         </is>
       </c>
       <c r="H172" s="10" t="n">
-        <v>0.000194980999992822</v>
+        <v>8.385300000668394e-05</v>
       </c>
       <c r="I172" s="7" t="inlineStr"/>
       <c r="J172" s="11" t="inlineStr">
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="H173" s="14" t="n">
-        <v>0.0001749630000063007</v>
+        <v>8.220000000846994e-05</v>
       </c>
       <c r="I173" s="4" t="inlineStr"/>
       <c r="J173" s="11" t="inlineStr">
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="H174" s="10" t="n">
-        <v>0.0001713770000009163</v>
+        <v>8.178400000247166e-05</v>
       </c>
       <c r="I174" s="7" t="inlineStr"/>
       <c r="J174" s="11" t="inlineStr">
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="H175" s="14" t="n">
-        <v>0.0001796119999966095</v>
+        <v>7.928899999853911e-05</v>
       </c>
       <c r="I175" s="4" t="inlineStr"/>
       <c r="J175" s="11" t="inlineStr">
@@ -9238,7 +9238,7 @@
         </is>
       </c>
       <c r="H176" s="10" t="n">
-        <v>0.0001805650000079595</v>
+        <v>8.302199999832283e-05</v>
       </c>
       <c r="I176" s="7" t="inlineStr"/>
       <c r="J176" s="11" t="inlineStr">
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="H177" s="14" t="n">
-        <v>0.0001869359999915332</v>
+        <v>7.902900000544832e-05</v>
       </c>
       <c r="I177" s="4" t="inlineStr"/>
       <c r="J177" s="11" t="inlineStr">
@@ -9330,7 +9330,7 @@
         </is>
       </c>
       <c r="H178" s="10" t="n">
-        <v>0.0001309020000093142</v>
+        <v>7.861999999647651e-05</v>
       </c>
       <c r="I178" s="7" t="inlineStr"/>
       <c r="J178" s="11" t="inlineStr">
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="H179" s="14" t="n">
-        <v>0.0001136000000059312</v>
+        <v>7.975999999132455e-05</v>
       </c>
       <c r="I179" s="4" t="inlineStr"/>
       <c r="J179" s="11" t="inlineStr">
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="H180" s="10" t="n">
-        <v>0.0001126290000001973</v>
+        <v>8.080399999244037e-05</v>
       </c>
       <c r="I180" s="7" t="inlineStr"/>
       <c r="J180" s="11" t="inlineStr">
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="H181" s="14" t="n">
-        <v>0.0001188100000035774</v>
+        <v>9.932500000786604e-05</v>
       </c>
       <c r="I181" s="4" t="inlineStr"/>
       <c r="J181" s="11" t="inlineStr">
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="H182" s="10" t="n">
-        <v>0.0001200220000043828</v>
+        <v>8.448000001237688e-05</v>
       </c>
       <c r="I182" s="7" t="inlineStr"/>
       <c r="J182" s="11" t="inlineStr">
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="H183" s="14" t="n">
-        <v>0.0001119869999968159</v>
+        <v>7.999899999333593e-05</v>
       </c>
       <c r="I183" s="4" t="inlineStr"/>
       <c r="J183" s="11" t="inlineStr">
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="H184" s="10" t="n">
-        <v>0.0001116259999918157</v>
+        <v>7.888800000444007e-05</v>
       </c>
       <c r="I184" s="7" t="inlineStr"/>
       <c r="J184" s="11" t="inlineStr">
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="H185" s="14" t="n">
-        <v>0.0001223569999950769</v>
+        <v>7.685100000287548e-05</v>
       </c>
       <c r="I185" s="4" t="inlineStr"/>
       <c r="J185" s="11" t="inlineStr">
@@ -9698,7 +9698,7 @@
         </is>
       </c>
       <c r="H186" s="10" t="n">
-        <v>0.0001584229999878062</v>
+        <v>8.416599999350183e-05</v>
       </c>
       <c r="I186" s="7" t="inlineStr"/>
       <c r="J186" s="11" t="inlineStr">
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="H187" s="14" t="n">
-        <v>0.0001095029999902408</v>
+        <v>7.914200000413985e-05</v>
       </c>
       <c r="I187" s="4" t="inlineStr"/>
       <c r="J187" s="11" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H188" s="10" t="n">
-        <v>0.0001085910000000467</v>
+        <v>7.860900001332993e-05</v>
       </c>
       <c r="I188" s="7" t="inlineStr"/>
       <c r="J188" s="11" t="inlineStr">
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="H189" s="14" t="n">
-        <v>0.0001072889999989002</v>
+        <v>7.771900000363985e-05</v>
       </c>
       <c r="I189" s="4" t="inlineStr"/>
       <c r="J189" s="11" t="inlineStr">
@@ -9882,7 +9882,7 @@
         </is>
       </c>
       <c r="H190" s="10" t="n">
-        <v>0.0001133600000002843</v>
+        <v>8.232899999427445e-05</v>
       </c>
       <c r="I190" s="7" t="inlineStr"/>
       <c r="J190" s="11" t="inlineStr">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="H191" s="14" t="n">
-        <v>0.0001085109999934275</v>
+        <v>7.87040000034267e-05</v>
       </c>
       <c r="I191" s="4" t="inlineStr"/>
       <c r="J191" s="11" t="inlineStr">
@@ -9974,7 +9974,7 @@
         </is>
       </c>
       <c r="H192" s="10" t="n">
-        <v>0.0001077690000101938</v>
+        <v>7.782999999506046e-05</v>
       </c>
       <c r="I192" s="7" t="inlineStr"/>
       <c r="J192" s="11" t="inlineStr">
@@ -10020,7 +10020,7 @@
         </is>
       </c>
       <c r="H193" s="14" t="n">
-        <v>0.0001076189999906774</v>
+        <v>8.284000000458036e-05</v>
       </c>
       <c r="I193" s="4" t="inlineStr"/>
       <c r="J193" s="11" t="inlineStr">
@@ -10066,7 +10066,7 @@
         </is>
       </c>
       <c r="H194" s="10" t="n">
-        <v>0.0001175679999931845</v>
+        <v>8.194900000546568e-05</v>
       </c>
       <c r="I194" s="7" t="inlineStr"/>
       <c r="J194" s="11" t="inlineStr">
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="H195" s="14" t="n">
-        <v>0.0001088920000000826</v>
+        <v>8.183100000280774e-05</v>
       </c>
       <c r="I195" s="4" t="inlineStr"/>
       <c r="J195" s="11" t="inlineStr">
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="H196" s="10" t="n">
-        <v>0.0001219560000009778</v>
+        <v>8.191900001008889e-05</v>
       </c>
       <c r="I196" s="7" t="inlineStr"/>
       <c r="J196" s="11" t="inlineStr">
@@ -10204,7 +10204,7 @@
         </is>
       </c>
       <c r="H197" s="14" t="n">
-        <v>0.0001170270000017126</v>
+        <v>7.958499999460855e-05</v>
       </c>
       <c r="I197" s="4" t="inlineStr"/>
       <c r="J197" s="11" t="inlineStr">
@@ -10250,7 +10250,7 @@
         </is>
       </c>
       <c r="H198" s="10" t="n">
-        <v>0.0001792019999982131</v>
+        <v>7.975300000850893e-05</v>
       </c>
       <c r="I198" s="7" t="inlineStr"/>
       <c r="J198" s="11" t="inlineStr">
@@ -10296,7 +10296,7 @@
         </is>
       </c>
       <c r="H199" s="14" t="n">
-        <v>0.0001132199999887007</v>
+        <v>7.77219999861245e-05</v>
       </c>
       <c r="I199" s="4" t="inlineStr"/>
       <c r="J199" s="11" t="inlineStr">
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="H200" s="10" t="n">
-        <v>0.0001076089999969554</v>
+        <v>8.14839999918604e-05</v>
       </c>
       <c r="I200" s="7" t="inlineStr"/>
       <c r="J200" s="11" t="inlineStr">
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="H201" s="14" t="n">
-        <v>0.0001068480000014915</v>
+        <v>7.721000000060485e-05</v>
       </c>
       <c r="I201" s="4" t="inlineStr"/>
       <c r="J201" s="11" t="inlineStr">
@@ -10434,7 +10434,7 @@
         </is>
       </c>
       <c r="H202" s="10" t="n">
-        <v>0.0001070980000008603</v>
+        <v>7.741800000360399e-05</v>
       </c>
       <c r="I202" s="7" t="inlineStr"/>
       <c r="J202" s="11" t="inlineStr">
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="H203" s="14" t="n">
-        <v>0.00010497399999565</v>
+        <v>7.749600000295231e-05</v>
       </c>
       <c r="I203" s="4" t="inlineStr"/>
       <c r="J203" s="11" t="inlineStr">
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="H204" s="10" t="n">
-        <v>0.0001054960000033134</v>
+        <v>7.661400000813501e-05</v>
       </c>
       <c r="I204" s="7" t="inlineStr"/>
       <c r="J204" s="11" t="inlineStr">
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="H205" s="14" t="n">
-        <v>0.0001143319999954429</v>
+        <v>7.842199998719934e-05</v>
       </c>
       <c r="I205" s="4" t="inlineStr"/>
       <c r="J205" s="11" t="inlineStr">
@@ -10618,7 +10618,7 @@
         </is>
       </c>
       <c r="H206" s="10" t="n">
-        <v>0.0001120780000007926</v>
+        <v>8.208699999556757e-05</v>
       </c>
       <c r="I206" s="7" t="inlineStr"/>
       <c r="J206" s="11" t="inlineStr">
@@ -10664,7 +10664,7 @@
         </is>
       </c>
       <c r="H207" s="14" t="n">
-        <v>0.0001295900000002348</v>
+        <v>8.065800000167656e-05</v>
       </c>
       <c r="I207" s="4" t="inlineStr"/>
       <c r="J207" s="11" t="inlineStr">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="H208" s="10" t="n">
-        <v>0.0001056959999914397</v>
+        <v>7.60670000090613e-05</v>
       </c>
       <c r="I208" s="7" t="inlineStr"/>
       <c r="J208" s="11" t="inlineStr">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="H209" s="14" t="n">
-        <v>0.0001035920000020951</v>
+        <v>7.86340000047403e-05</v>
       </c>
       <c r="I209" s="4" t="inlineStr"/>
       <c r="J209" s="11" t="inlineStr">
@@ -10802,7 +10802,7 @@
         </is>
       </c>
       <c r="H210" s="10" t="n">
-        <v>0.0001118870000027528</v>
+        <v>7.981599999595801e-05</v>
       </c>
       <c r="I210" s="7" t="inlineStr"/>
       <c r="J210" s="11" t="inlineStr">
@@ -10848,7 +10848,7 @@
         </is>
       </c>
       <c r="H211" s="14" t="n">
-        <v>0.0001109659999940504</v>
+        <v>7.973700000718509e-05</v>
       </c>
       <c r="I211" s="4" t="inlineStr"/>
       <c r="J211" s="11" t="inlineStr">
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="H212" s="10" t="n">
-        <v>0.000108049999994364</v>
+        <v>7.882299999550924e-05</v>
       </c>
       <c r="I212" s="7" t="inlineStr"/>
       <c r="J212" s="11" t="inlineStr">
@@ -10940,7 +10940,7 @@
         </is>
       </c>
       <c r="H213" s="14" t="n">
-        <v>0.0001081600000105709</v>
+        <v>7.684500000948447e-05</v>
       </c>
       <c r="I213" s="4" t="inlineStr"/>
       <c r="J213" s="11" t="inlineStr">
@@ -10986,7 +10986,7 @@
         </is>
       </c>
       <c r="H214" s="10" t="n">
-        <v>0.0001109049999996614</v>
+        <v>7.613200000378129e-05</v>
       </c>
       <c r="I214" s="7" t="inlineStr"/>
       <c r="J214" s="11" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="H215" s="14" t="n">
-        <v>0.000108791000002384</v>
+        <v>7.592199999351124e-05</v>
       </c>
       <c r="I215" s="4" t="inlineStr"/>
       <c r="J215" s="11" t="inlineStr">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="H216" s="10" t="n">
-        <v>0.0001384959999910507</v>
+        <v>7.967200001246511e-05</v>
       </c>
       <c r="I216" s="7" t="inlineStr"/>
       <c r="J216" s="11" t="inlineStr">
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="H217" s="14" t="n">
-        <v>0.0001098240000061423</v>
+        <v>8.113299999479295e-05</v>
       </c>
       <c r="I217" s="4" t="inlineStr"/>
       <c r="J217" s="11" t="inlineStr">
@@ -11170,7 +11170,7 @@
         </is>
       </c>
       <c r="H218" s="10" t="n">
-        <v>0.0001060959999961142</v>
+        <v>7.823200000700581e-05</v>
       </c>
       <c r="I218" s="7" t="inlineStr"/>
       <c r="J218" s="11" t="inlineStr">
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="H219" s="14" t="n">
-        <v>0.0001047840000012457</v>
+        <v>7.617400000015095e-05</v>
       </c>
       <c r="I219" s="4" t="inlineStr"/>
       <c r="J219" s="11" t="inlineStr">
@@ -11262,7 +11262,7 @@
         </is>
       </c>
       <c r="H220" s="10" t="n">
-        <v>0.0001057659999901261</v>
+        <v>8.173999999883108e-05</v>
       </c>
       <c r="I220" s="7" t="inlineStr"/>
       <c r="J220" s="11" t="inlineStr">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H221" s="14" t="n">
-        <v>0.0001049640000019281</v>
+        <v>7.67169999988937e-05</v>
       </c>
       <c r="I221" s="4" t="inlineStr"/>
       <c r="J221" s="11" t="inlineStr">
@@ -11354,7 +11354,7 @@
         </is>
       </c>
       <c r="H222" s="10" t="n">
-        <v>0.0001104849999933322</v>
+        <v>7.671900000616461e-05</v>
       </c>
       <c r="I222" s="7" t="inlineStr"/>
       <c r="J222" s="11" t="inlineStr">
@@ -11400,7 +11400,7 @@
         </is>
       </c>
       <c r="H223" s="14" t="n">
-        <v>0.000111627000009662</v>
+        <v>8.149100000309772e-05</v>
       </c>
       <c r="I223" s="4" t="inlineStr"/>
       <c r="J223" s="11" t="inlineStr">
@@ -11446,7 +11446,7 @@
         </is>
       </c>
       <c r="H224" s="10" t="n">
-        <v>0.0001322140000041827</v>
+        <v>7.641200001273774e-05</v>
       </c>
       <c r="I224" s="7" t="inlineStr"/>
       <c r="J224" s="11" t="inlineStr">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="H225" s="14" t="n">
-        <v>0.0001053750000039599</v>
+        <v>7.837199999016775e-05</v>
       </c>
       <c r="I225" s="4" t="inlineStr"/>
       <c r="J225" s="11" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="H226" s="10" t="n">
-        <v>0.0001049749999992855</v>
+        <v>7.693700000288572e-05</v>
       </c>
       <c r="I226" s="7" t="inlineStr"/>
       <c r="J226" s="11" t="inlineStr">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="H227" s="14" t="n">
-        <v>0.0001052850000036187</v>
+        <v>7.536999999047111e-05</v>
       </c>
       <c r="I227" s="4" t="inlineStr"/>
       <c r="J227" s="11" t="inlineStr">
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="H228" s="10" t="n">
-        <v>0.0001106349999986378</v>
+        <v>7.560500000636239e-05</v>
       </c>
       <c r="I228" s="7" t="inlineStr"/>
       <c r="J228" s="11" t="inlineStr">
@@ -11676,7 +11676,7 @@
         </is>
       </c>
       <c r="H229" s="14" t="n">
-        <v>0.0001053450000085832</v>
+        <v>8.281700000623005e-05</v>
       </c>
       <c r="I229" s="4" t="inlineStr"/>
       <c r="J229" s="11" t="inlineStr">
@@ -11722,7 +11722,7 @@
         </is>
       </c>
       <c r="H230" s="10" t="n">
-        <v>0.0001131990000118321</v>
+        <v>7.600600000046143e-05</v>
       </c>
       <c r="I230" s="7" t="inlineStr"/>
       <c r="J230" s="11" t="inlineStr">
@@ -11768,7 +11768,7 @@
         </is>
       </c>
       <c r="H231" s="14" t="n">
-        <v>0.0001079700000019557</v>
+        <v>7.547599999213617e-05</v>
       </c>
       <c r="I231" s="4" t="inlineStr"/>
       <c r="J231" s="11" t="inlineStr">
@@ -11814,7 +11814,7 @@
         </is>
       </c>
       <c r="H232" s="10" t="n">
-        <v>0.0001922659999991083</v>
+        <v>8.369300000765634e-05</v>
       </c>
       <c r="I232" s="7" t="inlineStr"/>
       <c r="J232" s="11" t="inlineStr">
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="H233" s="14" t="n">
-        <v>0.001144889000002536</v>
+        <v>0.0009176399999972773</v>
       </c>
       <c r="I233" s="4" t="inlineStr"/>
       <c r="J233" s="11" t="inlineStr">
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="H234" s="10" t="n">
-        <v>0.001015840999997408</v>
+        <v>0.0009232980000035695</v>
       </c>
       <c r="I234" s="7" t="inlineStr"/>
       <c r="J234" s="11" t="inlineStr">
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="H235" s="14" t="n">
-        <v>0.001000111000010406</v>
+        <v>0.0008788040000098363</v>
       </c>
       <c r="I235" s="4" t="inlineStr"/>
       <c r="J235" s="11" t="inlineStr">
@@ -11998,7 +11998,7 @@
         </is>
       </c>
       <c r="H236" s="10" t="n">
-        <v>0.0001335769999997183</v>
+        <v>8.250500000883676e-05</v>
       </c>
       <c r="I236" s="7" t="inlineStr"/>
       <c r="J236" s="11" t="inlineStr">
@@ -12044,7 +12044,7 @@
         </is>
       </c>
       <c r="H237" s="14" t="n">
-        <v>0.0001207939999972041</v>
+        <v>8.114199999909033e-05</v>
       </c>
       <c r="I237" s="4" t="inlineStr"/>
       <c r="J237" s="11" t="inlineStr">
@@ -12090,7 +12090,7 @@
         </is>
       </c>
       <c r="H238" s="10" t="n">
-        <v>0.0001135899999979983</v>
+        <v>8.737800000346851e-05</v>
       </c>
       <c r="I238" s="7" t="inlineStr"/>
       <c r="J238" s="11" t="inlineStr">
@@ -12136,7 +12136,7 @@
         </is>
       </c>
       <c r="H239" s="14" t="n">
-        <v>0.0001102639999999155</v>
+        <v>8.228400000120928e-05</v>
       </c>
       <c r="I239" s="4" t="inlineStr"/>
       <c r="J239" s="11" t="inlineStr">
@@ -12182,7 +12182,7 @@
         </is>
       </c>
       <c r="H240" s="10" t="n">
-        <v>0.0001106250000049158</v>
+        <v>8.30800000102272e-05</v>
       </c>
       <c r="I240" s="7" t="inlineStr"/>
       <c r="J240" s="11" t="inlineStr">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="H241" s="14" t="n">
-        <v>0.0001083100000016657</v>
+        <v>7.919899999819791e-05</v>
       </c>
       <c r="I241" s="4" t="inlineStr"/>
       <c r="J241" s="11" t="inlineStr">
@@ -12274,7 +12274,7 @@
         </is>
       </c>
       <c r="H242" s="10" t="n">
-        <v>0.0001124280000084354</v>
+        <v>8.150300000409061e-05</v>
       </c>
       <c r="I242" s="7" t="inlineStr"/>
       <c r="J242" s="11" t="inlineStr">
@@ -12320,7 +12320,7 @@
         </is>
       </c>
       <c r="H243" s="14" t="n">
-        <v>0.0009309930000114264</v>
+        <v>0.000774389000000042</v>
       </c>
       <c r="I243" s="4" t="inlineStr"/>
       <c r="J243" s="11" t="inlineStr">
@@ -12366,7 +12366,7 @@
         </is>
       </c>
       <c r="H244" s="10" t="n">
-        <v>0.0009798330000023725</v>
+        <v>0.0008648539999995819</v>
       </c>
       <c r="I244" s="7" t="inlineStr"/>
       <c r="J244" s="11" t="inlineStr">
@@ -12412,7 +12412,7 @@
         </is>
       </c>
       <c r="H245" s="14" t="n">
-        <v>0.001629285999996455</v>
+        <v>0.001274703000007094</v>
       </c>
       <c r="I245" s="4" t="inlineStr"/>
       <c r="J245" s="11" t="inlineStr">
@@ -12458,7 +12458,7 @@
         </is>
       </c>
       <c r="H246" s="10" t="n">
-        <v>0.0001119469999935063</v>
+        <v>8.315600000230461e-05</v>
       </c>
       <c r="I246" s="7" t="inlineStr"/>
       <c r="J246" s="11" t="inlineStr">
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="H247" s="14" t="n">
-        <v>0.0001108050000055982</v>
+        <v>8.05349999950522e-05</v>
       </c>
       <c r="I247" s="4" t="inlineStr"/>
       <c r="J247" s="11" t="inlineStr">
@@ -12550,7 +12550,7 @@
         </is>
       </c>
       <c r="H248" s="10" t="n">
-        <v>0.0001083709999960547</v>
+        <v>7.890400000576392e-05</v>
       </c>
       <c r="I248" s="7" t="inlineStr"/>
       <c r="J248" s="11" t="inlineStr">
@@ -12596,7 +12596,7 @@
         </is>
       </c>
       <c r="H249" s="14" t="n">
-        <v>0.0001144320000037169</v>
+        <v>7.853300000704166e-05</v>
       </c>
       <c r="I249" s="4" t="inlineStr"/>
       <c r="J249" s="11" t="inlineStr">
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="H250" s="10" t="n">
-        <v>0.0001324750000009089</v>
+        <v>8.423699999582368e-05</v>
       </c>
       <c r="I250" s="7" t="inlineStr"/>
       <c r="J250" s="11" t="inlineStr">
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="H251" s="14" t="n">
-        <v>0.0001080800000039517</v>
+        <v>8.081899999012876e-05</v>
       </c>
       <c r="I251" s="4" t="inlineStr"/>
       <c r="J251" s="11" t="inlineStr">
@@ -12734,7 +12734,7 @@
         </is>
       </c>
       <c r="H252" s="10" t="n">
-        <v>0.0001067569999975149</v>
+        <v>8.01300000006222e-05</v>
       </c>
       <c r="I252" s="7" t="inlineStr"/>
       <c r="J252" s="11" t="inlineStr">
@@ -12780,7 +12780,7 @@
         </is>
       </c>
       <c r="H253" s="14" t="n">
-        <v>0.0009904329999983474</v>
+        <v>0.0008522839999898224</v>
       </c>
       <c r="I253" s="4" t="inlineStr"/>
       <c r="J253" s="11" t="inlineStr">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H254" s="10" t="n">
-        <v>0.000975745999994615</v>
+        <v>0.0008204210000002377</v>
       </c>
       <c r="I254" s="7" t="inlineStr"/>
       <c r="J254" s="11" t="inlineStr">
@@ -12872,7 +12872,7 @@
         </is>
       </c>
       <c r="H255" s="14" t="n">
-        <v>0.0009522929999974394</v>
+        <v>0.0008364970000087624</v>
       </c>
       <c r="I255" s="4" t="inlineStr"/>
       <c r="J255" s="11" t="inlineStr">
@@ -12918,7 +12918,7 @@
         </is>
       </c>
       <c r="H256" s="10" t="n">
-        <v>0.0001117570000133128</v>
+        <v>8.306999998808351e-05</v>
       </c>
       <c r="I256" s="7" t="inlineStr"/>
       <c r="J256" s="11" t="inlineStr">
@@ -12964,7 +12964,7 @@
         </is>
       </c>
       <c r="H257" s="14" t="n">
-        <v>0.00011100599999736</v>
+        <v>9.797400001332335e-05</v>
       </c>
       <c r="I257" s="4" t="inlineStr"/>
       <c r="J257" s="11" t="inlineStr">
@@ -13010,7 +13010,7 @@
         </is>
       </c>
       <c r="H258" s="10" t="n">
-        <v>0.000109301999998479</v>
+        <v>8.024800000328014e-05</v>
       </c>
       <c r="I258" s="7" t="inlineStr"/>
       <c r="J258" s="11" t="inlineStr">
@@ -13056,7 +13056,7 @@
         </is>
       </c>
       <c r="H259" s="14" t="n">
-        <v>0.0001085209999871495</v>
+        <v>8.139399999151919e-05</v>
       </c>
       <c r="I259" s="4" t="inlineStr"/>
       <c r="J259" s="11" t="inlineStr">
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="H260" s="10" t="n">
-        <v>0.0001076890000035746</v>
+        <v>8.124699999711993e-05</v>
       </c>
       <c r="I260" s="7" t="inlineStr"/>
       <c r="J260" s="11" t="inlineStr">
@@ -13148,7 +13148,7 @@
         </is>
       </c>
       <c r="H261" s="14" t="n">
-        <v>0.0001082499999967013</v>
+        <v>7.763500001090051e-05</v>
       </c>
       <c r="I261" s="4" t="inlineStr"/>
       <c r="J261" s="11" t="inlineStr">
@@ -13194,7 +13194,7 @@
         </is>
       </c>
       <c r="H262" s="10" t="n">
-        <v>0.0001137809999960382</v>
+        <v>7.792399999573263e-05</v>
       </c>
       <c r="I262" s="7" t="inlineStr"/>
       <c r="J262" s="11" t="inlineStr">
@@ -13240,7 +13240,7 @@
         </is>
       </c>
       <c r="H263" s="14" t="n">
-        <v>0.0001164350000095737</v>
+        <v>8.293199999798162e-05</v>
       </c>
       <c r="I263" s="4" t="inlineStr"/>
       <c r="J263" s="11" t="inlineStr">
@@ -13286,7 +13286,7 @@
         </is>
       </c>
       <c r="H264" s="10" t="n">
-        <v>0.0001377150000081429</v>
+        <v>7.960199999956785e-05</v>
       </c>
       <c r="I264" s="7" t="inlineStr"/>
       <c r="J264" s="11" t="inlineStr">
@@ -13332,7 +13332,7 @@
         </is>
       </c>
       <c r="H265" s="14" t="n">
-        <v>0.0001101840000075072</v>
+        <v>8.653999999808093e-05</v>
       </c>
       <c r="I265" s="4" t="inlineStr"/>
       <c r="J265" s="11" t="inlineStr">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="H266" s="10" t="n">
-        <v>0.000112096999998812</v>
+        <v>8.531299999958719e-05</v>
       </c>
       <c r="I266" s="7" t="inlineStr"/>
       <c r="J266" s="11" t="inlineStr">
@@ -13424,7 +13424,7 @@
         </is>
       </c>
       <c r="H267" s="14" t="n">
-        <v>0.0001120069999984707</v>
+        <v>9.925199999827328e-05</v>
       </c>
       <c r="I267" s="4" t="inlineStr"/>
       <c r="J267" s="11" t="inlineStr">
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="H268" s="10" t="n">
-        <v>0.0001128079999972442</v>
+        <v>8.426499999814041e-05</v>
       </c>
       <c r="I268" s="7" t="inlineStr"/>
       <c r="J268" s="11" t="inlineStr">
@@ -13516,7 +13516,7 @@
         </is>
       </c>
       <c r="H269" s="14" t="n">
-        <v>0.0001113860000003797</v>
+        <v>8.162999999683507e-05</v>
       </c>
       <c r="I269" s="4" t="inlineStr"/>
       <c r="J269" s="11" t="inlineStr">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="H270" s="10" t="n">
-        <v>0.0001134299999989707</v>
+        <v>8.593600000494916e-05</v>
       </c>
       <c r="I270" s="7" t="inlineStr"/>
       <c r="J270" s="11" t="inlineStr">
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="H271" s="14" t="n">
-        <v>0.0001143409999997402</v>
+        <v>7.867700000474542e-05</v>
       </c>
       <c r="I271" s="4" t="inlineStr"/>
       <c r="J271" s="11" t="inlineStr">
@@ -13654,7 +13654,7 @@
         </is>
       </c>
       <c r="H272" s="10" t="n">
-        <v>0.0001096830000051341</v>
+        <v>8.10610000030465e-05</v>
       </c>
       <c r="I272" s="7" t="inlineStr"/>
       <c r="J272" s="11" t="inlineStr">
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="H273" s="14" t="n">
-        <v>0.0001129990000094949</v>
+        <v>8.599400000264268e-05</v>
       </c>
       <c r="I273" s="4" t="inlineStr"/>
       <c r="J273" s="11" t="inlineStr">
@@ -13746,7 +13746,7 @@
         </is>
       </c>
       <c r="H274" s="10" t="n">
-        <v>0.0001317029999938768</v>
+        <v>8.679100000108519e-05</v>
       </c>
       <c r="I274" s="7" t="inlineStr"/>
       <c r="J274" s="11" t="inlineStr">
@@ -13792,7 +13792,7 @@
         </is>
       </c>
       <c r="H275" s="14" t="n">
-        <v>0.0001092319999997926</v>
+        <v>9.186600000532508e-05</v>
       </c>
       <c r="I275" s="4" t="inlineStr"/>
       <c r="J275" s="11" t="inlineStr">
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="H276" s="10" t="n">
-        <v>0.0001090519999991102</v>
+        <v>8.194300001207466e-05</v>
       </c>
       <c r="I276" s="7" t="inlineStr"/>
       <c r="J276" s="11" t="inlineStr">
@@ -13884,7 +13884,7 @@
         </is>
       </c>
       <c r="H277" s="14" t="n">
-        <v>0.0001163250000075777</v>
+        <v>0.0001086030000010396</v>
       </c>
       <c r="I277" s="4" t="inlineStr"/>
       <c r="J277" s="11" t="inlineStr">
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="H278" s="10" t="n">
-        <v>0.0001081700000042929</v>
+        <v>7.968499998867173e-05</v>
       </c>
       <c r="I278" s="7" t="inlineStr"/>
       <c r="J278" s="11" t="inlineStr">
@@ -13976,7 +13976,7 @@
         </is>
       </c>
       <c r="H279" s="14" t="n">
-        <v>0.0001139709999904426</v>
+        <v>8.729500000015378e-05</v>
       </c>
       <c r="I279" s="4" t="inlineStr"/>
       <c r="J279" s="11" t="inlineStr">
@@ -14022,7 +14022,7 @@
         </is>
       </c>
       <c r="H280" s="10" t="n">
-        <v>0.0001148829999948475</v>
+        <v>8.767999999292897e-05</v>
       </c>
       <c r="I280" s="7" t="inlineStr"/>
       <c r="J280" s="11" t="inlineStr">
@@ -14068,7 +14068,7 @@
         </is>
       </c>
       <c r="H281" s="14" t="n">
-        <v>0.0001130590000002485</v>
+        <v>8.003899999664554e-05</v>
       </c>
       <c r="I281" s="4" t="inlineStr"/>
       <c r="J281" s="11" t="inlineStr">
@@ -14114,7 +14114,7 @@
         </is>
       </c>
       <c r="H282" s="10" t="n">
-        <v>0.0001401100000038014</v>
+        <v>8.34880000013527e-05</v>
       </c>
       <c r="I282" s="7" t="inlineStr"/>
       <c r="J282" s="11" t="inlineStr">
@@ -14160,7 +14160,7 @@
         </is>
       </c>
       <c r="H283" s="14" t="n">
-        <v>0.0001145609999895214</v>
+        <v>8.148899999582682e-05</v>
       </c>
       <c r="I283" s="4" t="inlineStr"/>
       <c r="J283" s="11" t="inlineStr">
@@ -14206,7 +14206,7 @@
         </is>
       </c>
       <c r="H284" s="10" t="n">
-        <v>0.000113620000007586</v>
+        <v>9.813600000541101e-05</v>
       </c>
       <c r="I284" s="7" t="inlineStr"/>
       <c r="J284" s="11" t="inlineStr">
@@ -14252,7 +14252,7 @@
         </is>
       </c>
       <c r="H285" s="14" t="n">
-        <v>0.0001091019999961418</v>
+        <v>0.0001038709999932053</v>
       </c>
       <c r="I285" s="4" t="inlineStr"/>
       <c r="J285" s="11" t="inlineStr">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="H286" s="10" t="n">
-        <v>0.0001074879999976019</v>
+        <v>8.574899999302943e-05</v>
       </c>
       <c r="I286" s="7" t="inlineStr"/>
       <c r="J286" s="11" t="inlineStr">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H287" s="14" t="n">
-        <v>0.0001080199999989873</v>
+        <v>8.096800000600979e-05</v>
       </c>
       <c r="I287" s="4" t="inlineStr"/>
       <c r="J287" s="11" t="inlineStr">
@@ -14390,7 +14390,7 @@
         </is>
       </c>
       <c r="H288" s="10" t="n">
-        <v>0.0001132090000055541</v>
+        <v>8.151000000111708e-05</v>
       </c>
       <c r="I288" s="7" t="inlineStr"/>
       <c r="J288" s="11" t="inlineStr">
@@ -14436,7 +14436,7 @@
         </is>
       </c>
       <c r="H289" s="14" t="n">
-        <v>0.0001340480000067146</v>
+        <v>8.045100000231287e-05</v>
       </c>
       <c r="I289" s="4" t="inlineStr"/>
       <c r="J289" s="11" t="inlineStr">
@@ -14482,7 +14482,7 @@
         </is>
       </c>
       <c r="H290" s="10" t="n">
-        <v>0.0001165160000056176</v>
+        <v>8.050099999934446e-05</v>
       </c>
       <c r="I290" s="7" t="inlineStr"/>
       <c r="J290" s="11" t="inlineStr">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="H291" s="14" t="n">
-        <v>0.0001077800000075513</v>
+        <v>8.371200000567569e-05</v>
       </c>
       <c r="I291" s="4" t="inlineStr"/>
       <c r="J291" s="11" t="inlineStr">
@@ -14574,7 +14574,7 @@
         </is>
       </c>
       <c r="H292" s="10" t="n">
-        <v>0.000108399999987796</v>
+        <v>8.35929999993823e-05</v>
       </c>
       <c r="I292" s="7" t="inlineStr"/>
       <c r="J292" s="11" t="inlineStr">
@@ -14620,7 +14620,7 @@
         </is>
       </c>
       <c r="H293" s="14" t="n">
-        <v>0.0001142010000023674</v>
+        <v>8.673699998951179e-05</v>
       </c>
       <c r="I293" s="4" t="inlineStr"/>
       <c r="J293" s="11" t="inlineStr">
@@ -14666,7 +14666,7 @@
         </is>
       </c>
       <c r="H294" s="10" t="n">
-        <v>0.0001184889999876759</v>
+        <v>8.380300000965235e-05</v>
       </c>
       <c r="I294" s="7" t="inlineStr"/>
       <c r="J294" s="11" t="inlineStr">
@@ -14712,7 +14712,7 @@
         </is>
       </c>
       <c r="H295" s="14" t="n">
-        <v>0.0001162049999976489</v>
+        <v>8.143499999846426e-05</v>
       </c>
       <c r="I295" s="4" t="inlineStr"/>
       <c r="J295" s="11" t="inlineStr">
@@ -14758,7 +14758,7 @@
         </is>
       </c>
       <c r="H296" s="10" t="n">
-        <v>0.0001103940000035664</v>
+        <v>8.408799999415351e-05</v>
       </c>
       <c r="I296" s="7" t="inlineStr"/>
       <c r="J296" s="11" t="inlineStr">
@@ -14804,7 +14804,7 @@
         </is>
       </c>
       <c r="H297" s="14" t="n">
-        <v>0.0001099340000081384</v>
+        <v>8.785900000418678e-05</v>
       </c>
       <c r="I297" s="4" t="inlineStr"/>
       <c r="J297" s="11" t="inlineStr">
@@ -14850,7 +14850,7 @@
         </is>
       </c>
       <c r="H298" s="10" t="n">
-        <v>0.0001107749999960106</v>
+        <v>8.405299999481031e-05</v>
       </c>
       <c r="I298" s="7" t="inlineStr"/>
       <c r="J298" s="11" t="inlineStr">
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="H299" s="14" t="n">
-        <v>0.0001123570000061136</v>
+        <v>8.005900001251121e-05</v>
       </c>
       <c r="I299" s="4" t="inlineStr"/>
       <c r="J299" s="11" t="inlineStr">
@@ -14942,7 +14942,7 @@
         </is>
       </c>
       <c r="H300" s="10" t="n">
-        <v>0.000140771000005202</v>
+        <v>8.777600000087205e-05</v>
       </c>
       <c r="I300" s="7" t="inlineStr"/>
       <c r="J300" s="11" t="inlineStr">
@@ -14988,7 +14988,7 @@
         </is>
       </c>
       <c r="H301" s="14" t="n">
-        <v>0.0001137610000085942</v>
+        <v>8.025399999667115e-05</v>
       </c>
       <c r="I301" s="4" t="inlineStr"/>
       <c r="J301" s="11" t="inlineStr">
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="H302" s="10" t="n">
-        <v>0.0001080799999897408</v>
+        <v>8.073099999705846e-05</v>
       </c>
       <c r="I302" s="7" t="inlineStr"/>
       <c r="J302" s="11" t="inlineStr">
@@ -15080,7 +15080,7 @@
         </is>
       </c>
       <c r="H303" s="14" t="n">
-        <v>0.0001068379999935587</v>
+        <v>8.248000000321554e-05</v>
       </c>
       <c r="I303" s="4" t="inlineStr"/>
       <c r="J303" s="11" t="inlineStr">
@@ -15126,7 +15126,7 @@
         </is>
       </c>
       <c r="H304" s="10" t="n">
-        <v>0.0001078300000045829</v>
+        <v>8.482900000217342e-05</v>
       </c>
       <c r="I304" s="7" t="inlineStr"/>
       <c r="J304" s="11" t="inlineStr">
@@ -15172,7 +15172,7 @@
         </is>
       </c>
       <c r="H305" s="14" t="n">
-        <v>0.0001086010000079796</v>
+        <v>8.010500000921184e-05</v>
       </c>
       <c r="I305" s="4" t="inlineStr"/>
       <c r="J305" s="11" t="inlineStr">
@@ -15218,7 +15218,7 @@
         </is>
       </c>
       <c r="H306" s="10" t="n">
-        <v>0.000115563999997903</v>
+        <v>8.005800000887575e-05</v>
       </c>
       <c r="I306" s="7" t="inlineStr"/>
       <c r="J306" s="11" t="inlineStr">
@@ -15264,7 +15264,7 @@
         </is>
       </c>
       <c r="H307" s="14" t="n">
-        <v>0.0001255520000000843</v>
+        <v>8.617599999638514e-05</v>
       </c>
       <c r="I307" s="4" t="inlineStr"/>
       <c r="J307" s="11" t="inlineStr">
@@ -15310,7 +15310,7 @@
         </is>
       </c>
       <c r="H308" s="10" t="n">
-        <v>0.000137304000006111</v>
+        <v>8.094800000435498e-05</v>
       </c>
       <c r="I308" s="7" t="inlineStr"/>
       <c r="J308" s="11" t="inlineStr">
@@ -15356,7 +15356,7 @@
         </is>
       </c>
       <c r="H309" s="14" t="n">
-        <v>0.0001080700000102297</v>
+        <v>8.545100000389994e-05</v>
       </c>
       <c r="I309" s="4" t="inlineStr"/>
       <c r="J309" s="11" t="inlineStr">
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="H310" s="10" t="n">
-        <v>0.0001084609999963959</v>
+        <v>8.36629999980687e-05</v>
       </c>
       <c r="I310" s="7" t="inlineStr"/>
       <c r="J310" s="11" t="inlineStr">
@@ -15448,7 +15448,7 @@
         </is>
       </c>
       <c r="H311" s="14" t="n">
-        <v>0.0001073790000134522</v>
+        <v>7.97400000038806e-05</v>
       </c>
       <c r="I311" s="4" t="inlineStr"/>
       <c r="J311" s="11" t="inlineStr">
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="H312" s="10" t="n">
-        <v>0.000113500000011868</v>
+        <v>8.054600000662049e-05</v>
       </c>
       <c r="I312" s="7" t="inlineStr"/>
       <c r="J312" s="11" t="inlineStr">
@@ -15540,7 +15540,7 @@
         </is>
       </c>
       <c r="H313" s="14" t="n">
-        <v>0.000107538999998269</v>
+        <v>8.00229999953217e-05</v>
       </c>
       <c r="I313" s="4" t="inlineStr"/>
       <c r="J313" s="11" t="inlineStr">
@@ -15586,7 +15586,7 @@
         </is>
       </c>
       <c r="H314" s="10" t="n">
-        <v>0.0001070779999992055</v>
+        <v>7.886299999881885e-05</v>
       </c>
       <c r="I314" s="7" t="inlineStr"/>
       <c r="J314" s="11" t="inlineStr">
@@ -15632,7 +15632,7 @@
         </is>
       </c>
       <c r="H315" s="14" t="n">
-        <v>0.0001089710000030664</v>
+        <v>8.253299999694264e-05</v>
       </c>
       <c r="I315" s="4" t="inlineStr"/>
       <c r="J315" s="11" t="inlineStr">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="H316" s="10" t="n">
-        <v>0.0001349599999969087</v>
+        <v>8.211699999094435e-05</v>
       </c>
       <c r="I316" s="7" t="inlineStr"/>
       <c r="J316" s="11" t="inlineStr">
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="H317" s="14" t="n">
-        <v>0.0001039330000054406</v>
+        <v>7.746100000360912e-05</v>
       </c>
       <c r="I317" s="4" t="inlineStr"/>
       <c r="J317" s="11" t="inlineStr">
@@ -15770,7 +15770,7 @@
         </is>
       </c>
       <c r="H318" s="10" t="n">
-        <v>0.000115163000003804</v>
+        <v>8.184100001074057e-05</v>
       </c>
       <c r="I318" s="7" t="inlineStr"/>
       <c r="J318" s="11" t="inlineStr">
@@ -15816,7 +15816,7 @@
         </is>
       </c>
       <c r="H319" s="14" t="n">
-        <v>0.0001182590000041728</v>
+        <v>8.027300000890136e-05</v>
       </c>
       <c r="I319" s="4" t="inlineStr"/>
       <c r="J319" s="11" t="inlineStr">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H320" s="10" t="n">
-        <v>0.0001068469999978561</v>
+        <v>8.381000000667882e-05</v>
       </c>
       <c r="I320" s="7" t="inlineStr"/>
       <c r="J320" s="11" t="inlineStr">
@@ -15908,7 +15908,7 @@
         </is>
       </c>
       <c r="H321" s="14" t="n">
-        <v>0.0001066579999928763</v>
+        <v>8.042000000330063e-05</v>
       </c>
       <c r="I321" s="4" t="inlineStr"/>
       <c r="J321" s="11" t="inlineStr">
@@ -15954,7 +15954,7 @@
         </is>
       </c>
       <c r="H322" s="10" t="n">
-        <v>0.0001055859999894437</v>
+        <v>7.753300000956642e-05</v>
       </c>
       <c r="I322" s="7" t="inlineStr"/>
       <c r="J322" s="11" t="inlineStr">
@@ -16000,7 +16000,7 @@
         </is>
       </c>
       <c r="H323" s="14" t="n">
-        <v>0.0001097829999991973</v>
+        <v>7.990699999993467e-05</v>
       </c>
       <c r="I323" s="4" t="inlineStr"/>
       <c r="J323" s="11" t="inlineStr">
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="H324" s="10" t="n">
-        <v>0.0001498369999950455</v>
+        <v>7.781099999704111e-05</v>
       </c>
       <c r="I324" s="7" t="inlineStr"/>
       <c r="J324" s="11" t="inlineStr">
@@ -16092,7 +16092,7 @@
         </is>
       </c>
       <c r="H325" s="14" t="n">
-        <v>0.0001037610000054201</v>
+        <v>8.02690000085704e-05</v>
       </c>
       <c r="I325" s="4" t="inlineStr"/>
       <c r="J325" s="11" t="inlineStr">
@@ -16138,7 +16138,7 @@
         </is>
       </c>
       <c r="H326" s="10" t="n">
-        <v>0.0002115319999944631</v>
+        <v>7.711700000356814e-05</v>
       </c>
       <c r="I326" s="7" t="inlineStr"/>
       <c r="J326" s="11" t="inlineStr">
@@ -16184,7 +16184,7 @@
         </is>
       </c>
       <c r="H327" s="14" t="n">
-        <v>0.0001196719999967399</v>
+        <v>8.098500001096909e-05</v>
       </c>
       <c r="I327" s="4" t="inlineStr"/>
       <c r="J327" s="11" t="inlineStr">
@@ -16230,7 +16230,7 @@
         </is>
       </c>
       <c r="H328" s="10" t="n">
-        <v>0.0001586839999987433</v>
+        <v>7.698000000289085e-05</v>
       </c>
       <c r="I328" s="7" t="inlineStr"/>
       <c r="J328" s="11" t="inlineStr">
@@ -16276,7 +16276,7 @@
         </is>
       </c>
       <c r="H329" s="14" t="n">
-        <v>0.0001386459999963563</v>
+        <v>7.664399998930094e-05</v>
       </c>
       <c r="I329" s="4" t="inlineStr"/>
       <c r="J329" s="11" t="inlineStr">
@@ -16322,7 +16322,7 @@
         </is>
       </c>
       <c r="H330" s="10" t="n">
-        <v>0.0001117170000100032</v>
+        <v>7.691800000486637e-05</v>
       </c>
       <c r="I330" s="7" t="inlineStr"/>
       <c r="J330" s="11" t="inlineStr">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="H331" s="14" t="n">
-        <v>0.0001073490000038646</v>
+        <v>7.782100000497394e-05</v>
       </c>
       <c r="I331" s="4" t="inlineStr"/>
       <c r="J331" s="11" t="inlineStr">
@@ -16414,7 +16414,7 @@
         </is>
       </c>
       <c r="H332" s="10" t="n">
-        <v>0.0001063269999974636</v>
+        <v>7.693199999891931e-05</v>
       </c>
       <c r="I332" s="7" t="inlineStr"/>
       <c r="J332" s="11" t="inlineStr">
@@ -16460,7 +16460,7 @@
         </is>
       </c>
       <c r="H333" s="14" t="n">
-        <v>0.000111125999993078</v>
+        <v>8.631500000433334e-05</v>
       </c>
       <c r="I333" s="4" t="inlineStr"/>
       <c r="J333" s="11" t="inlineStr">
@@ -16506,7 +16506,7 @@
         </is>
       </c>
       <c r="H334" s="10" t="n">
-        <v>0.0001084199999894508</v>
+        <v>7.888800000444007e-05</v>
       </c>
       <c r="I334" s="7" t="inlineStr"/>
       <c r="J334" s="11" t="inlineStr">
@@ -16552,7 +16552,7 @@
         </is>
       </c>
       <c r="H335" s="14" t="n">
-        <v>0.0001080199999989873</v>
+        <v>7.871800001169049e-05</v>
       </c>
       <c r="I335" s="4" t="inlineStr"/>
       <c r="J335" s="11" t="inlineStr">
@@ -16598,7 +16598,7 @@
         </is>
       </c>
       <c r="H336" s="10" t="n">
-        <v>0.0001119169999981295</v>
+        <v>7.997400000192556e-05</v>
       </c>
       <c r="I336" s="7" t="inlineStr"/>
       <c r="J336" s="11" t="inlineStr">
@@ -16644,7 +16644,7 @@
         </is>
       </c>
       <c r="H337" s="14" t="n">
-        <v>0.0001081599999963601</v>
+        <v>7.744000001252971e-05</v>
       </c>
       <c r="I337" s="4" t="inlineStr"/>
       <c r="J337" s="11" t="inlineStr">
@@ -16690,7 +16690,7 @@
         </is>
       </c>
       <c r="H338" s="10" t="n">
-        <v>0.0001329260000062504</v>
+        <v>7.744299999501436e-05</v>
       </c>
       <c r="I338" s="7" t="inlineStr"/>
       <c r="J338" s="11" t="inlineStr">
@@ -16736,7 +16736,7 @@
         </is>
       </c>
       <c r="H339" s="14" t="n">
-        <v>0.0001058059999934358</v>
+        <v>8.264899999232966e-05</v>
       </c>
       <c r="I339" s="4" t="inlineStr"/>
       <c r="J339" s="11" t="inlineStr">
@@ -16782,7 +16782,7 @@
         </is>
       </c>
       <c r="H340" s="10" t="n">
-        <v>0.000112047999991205</v>
+        <v>8.407700001100693e-05</v>
       </c>
       <c r="I340" s="7" t="inlineStr"/>
       <c r="J340" s="11" t="inlineStr">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="H341" s="14" t="n">
-        <v>0.0001051549999999679</v>
+        <v>7.641199999852688e-05</v>
       </c>
       <c r="I341" s="4" t="inlineStr"/>
       <c r="J341" s="11" t="inlineStr">
@@ -16874,7 +16874,7 @@
         </is>
       </c>
       <c r="H342" s="10" t="n">
-        <v>0.0001102740000078484</v>
+        <v>7.82479999941188e-05</v>
       </c>
       <c r="I342" s="7" t="inlineStr"/>
       <c r="J342" s="11" t="inlineStr">
@@ -16920,7 +16920,7 @@
         </is>
       </c>
       <c r="H343" s="14" t="n">
-        <v>0.0001061359999994238</v>
+        <v>7.999999999697138e-05</v>
       </c>
       <c r="I343" s="4" t="inlineStr"/>
       <c r="J343" s="11" t="inlineStr">
@@ -16966,7 +16966,7 @@
         </is>
       </c>
       <c r="H344" s="10" t="n">
-        <v>0.000105485000005956</v>
+        <v>7.744199999137891e-05</v>
       </c>
       <c r="I344" s="7" t="inlineStr"/>
       <c r="J344" s="11" t="inlineStr">
@@ -17012,7 +17012,7 @@
         </is>
       </c>
       <c r="H345" s="14" t="n">
-        <v>0.0001076499999896896</v>
+        <v>8.115300001065862e-05</v>
       </c>
       <c r="I345" s="4" t="inlineStr"/>
       <c r="J345" s="11" t="inlineStr">
@@ -17058,7 +17058,7 @@
         </is>
       </c>
       <c r="H346" s="10" t="n">
-        <v>0.0001292590000048222</v>
+        <v>9.175300000663356e-05</v>
       </c>
       <c r="I346" s="7" t="inlineStr"/>
       <c r="J346" s="11" t="inlineStr">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="H347" s="14" t="n">
-        <v>0.0001059159999954318</v>
+        <v>7.676100000253427e-05</v>
       </c>
       <c r="I347" s="4" t="inlineStr"/>
       <c r="J347" s="11" t="inlineStr">
@@ -17150,7 +17150,7 @@
         </is>
       </c>
       <c r="H348" s="10" t="n">
-        <v>0.0001102850000052058</v>
+        <v>7.820100000799357e-05</v>
       </c>
       <c r="I348" s="7" t="inlineStr"/>
       <c r="J348" s="11" t="inlineStr">
@@ -17196,7 +17196,7 @@
         </is>
       </c>
       <c r="H349" s="14" t="n">
-        <v>0.0001163149999996449</v>
+        <v>8.111200000371355e-05</v>
       </c>
       <c r="I349" s="4" t="inlineStr"/>
       <c r="J349" s="11" t="inlineStr">
@@ -17242,7 +17242,7 @@
         </is>
       </c>
       <c r="H350" s="10" t="n">
-        <v>0.0001080199999989873</v>
+        <v>7.889799999816205e-05</v>
       </c>
       <c r="I350" s="7" t="inlineStr"/>
       <c r="J350" s="11" t="inlineStr">
@@ -17288,7 +17288,7 @@
         </is>
       </c>
       <c r="H351" s="14" t="n">
-        <v>0.000106115999997769</v>
+        <v>8.28010000049062e-05</v>
       </c>
       <c r="I351" s="4" t="inlineStr"/>
       <c r="J351" s="11" t="inlineStr">
@@ -17334,7 +17334,7 @@
         </is>
       </c>
       <c r="H352" s="10" t="n">
-        <v>0.0001164049999999861</v>
+        <v>8.225499999525709e-05</v>
       </c>
       <c r="I352" s="7" t="inlineStr"/>
       <c r="J352" s="11" t="inlineStr">
